--- a/summary/results.xlsx
+++ b/summary/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOUTORADO\units\XAI4Spectra\summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84620DA-8F4E-4C8D-A854-760B77BE8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F25C40-0C8A-4E34-B33E-2E45AD442BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{186261AE-5D16-4F15-B298-8943B4C3693F}"/>
   </bookViews>
